--- a/数据表/Datas/EnemyPartyConfig_敌人队伍配置.xlsx
+++ b/数据表/Datas/EnemyPartyConfig_敌人队伍配置.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Seek-Battle-Evacuate\数据表\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -72,7 +77,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人队伍</t>
@@ -81,7 +86,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>ID</t>
@@ -92,7 +97,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>显示名</t>
@@ -103,7 +108,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>按顺序进入战斗的敌人</t>
@@ -112,7 +117,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>ID</t>
@@ -121,7 +126,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>，最多</t>
@@ -130,7 +135,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>4</t>
@@ -139,7 +144,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>个</t>
@@ -150,7 +155,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>威胁等级</t>
@@ -161,7 +166,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>单敌人</t>
@@ -171,14 +176,21 @@
     <t>3001</t>
   </si>
   <si>
-    <t>低</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>低</t>
+    </r>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>双普通敌人</t>
@@ -192,7 +204,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>混合队伍</t>
@@ -202,14 +214,21 @@
     <t>3001,3002</t>
   </si>
   <si>
-    <t>中</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中</t>
+    </r>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>高威胁队伍</t>
@@ -219,13 +238,20 @@
     <t>3002,3003</t>
   </si>
   <si>
-    <t>高</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>四普通敌人</t>
@@ -245,7 +271,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -253,42 +279,37 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF006100"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F4E78"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF595959"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体-简"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -444,19 +465,19 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="PingFang SC Regular"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -852,153 +873,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1051,9 +1072,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -1531,10 +1549,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7205882352941" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.9044117647059" style="2" customWidth="1"/>
-    <col min="4" max="4" width="41.9044117647059" style="3" customWidth="1"/>
-    <col min="5" max="5" width="53.3014705882353" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.7166666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.9083333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="41.9083333333333" style="3" customWidth="1"/>
+    <col min="5" max="5" width="53.3" style="2" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1617,7 +1635,7 @@
       <c r="D5" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1638,7 +1656,7 @@
       <c r="D7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1659,7 +1677,7 @@
       <c r="D9" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1680,7 +1698,7 @@
       <c r="D11" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="2" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1694,10 +1712,10 @@
       <c r="C13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="2" t="s">
         <v>27</v>
       </c>
     </row>

--- a/数据表/Datas/EnemyPartyConfig_敌人队伍配置.xlsx
+++ b/数据表/Datas/EnemyPartyConfig_敌人队伍配置.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -173,7 +173,7 @@
     </r>
   </si>
   <si>
-    <t>3001</t>
+    <t>3001,3001,3001</t>
   </si>
   <si>
     <r>
@@ -193,11 +193,11 @@
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
-      <t>双普通敌人</t>
+      <t>三普通敌人</t>
     </r>
   </si>
   <si>
-    <t>3001,3001</t>
+    <t>3001,3002</t>
   </si>
   <si>
     <r>
@@ -211,7 +211,7 @@
     </r>
   </si>
   <si>
-    <t>3001,3002</t>
+    <t>3001,3002,3002</t>
   </si>
   <si>
     <r>
@@ -231,11 +231,25 @@
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
-      <t>高威胁队伍</t>
+      <t>敌人</t>
     </r>
   </si>
   <si>
-    <t>3002,3003</t>
+    <t>3002,3001,3002</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>威胁队伍</t>
+    </r>
+  </si>
+  <si>
+    <t>3002,3002,3002</t>
   </si>
   <si>
     <r>
@@ -258,7 +272,17 @@
     </r>
   </si>
   <si>
-    <t>3001,3002,3001,3002</t>
+    <t>3001,3001,3001,3001</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>威胁队伍</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -465,18 +489,18 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1019,7 +1043,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1070,10 +1094,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1545,7 +1582,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -1632,7 +1669,7 @@
       <c r="C5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="21" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -1643,7 +1680,7 @@
       <c r="A6" s="16"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
-      <c r="D6" s="18"/>
+      <c r="D6" s="19"/>
     </row>
     <row r="7" customHeight="1" spans="1:5">
       <c r="A7" s="16"/>
@@ -1653,7 +1690,7 @@
       <c r="C7" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="22" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -1664,17 +1701,17 @@
       <c r="A8" s="16"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
-      <c r="D8" s="18"/>
+      <c r="D8" s="19"/>
     </row>
     <row r="9" customHeight="1" spans="1:5">
       <c r="A9" s="16"/>
       <c r="B9" s="17">
-        <v>4003</v>
+        <v>4101</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="22" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -1685,38 +1722,79 @@
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
-      <c r="D10" s="18"/>
+      <c r="D10" s="19"/>
     </row>
     <row r="11" customHeight="1" spans="1:5">
       <c r="A11" s="16"/>
       <c r="B11" s="17">
-        <v>4004</v>
+        <v>4102</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="22" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:5">
-      <c r="D12" s="1"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="19"/>
     </row>
     <row r="13" customHeight="1" spans="1:5">
-      <c r="B13" s="2">
-        <v>4005</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="A13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="19"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:5">
+      <c r="A14" s="16"/>
+      <c r="B14" s="17">
+        <v>4201</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="E14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>27</v>
+    </row>
+    <row r="15" customHeight="1" spans="1:5">
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:5">
+      <c r="B16" s="2">
+        <v>4202</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="2:5">
+      <c r="B18" s="2">
+        <v>4203</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
